--- a/experiments/mogao_data_measured_consolidated.xlsx
+++ b/experiments/mogao_data_measured_consolidated.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="43425" yWindow="2910" windowWidth="28800" windowHeight="15285" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,28 +12,65 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Azurite" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
-    <font/>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -46,7 +82,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00365F91"/>
+        <fgColor rgb="FF365F91"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,14 +98,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -433,7 +471,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
@@ -446,7 +484,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -470,7 +508,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
+      <c r="A6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -480,7 +518,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -511,7 +549,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
+      <c r="A13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -528,7 +566,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
+      <c r="A16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -598,7 +636,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M141"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -608,9 +646,7 @@
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="9" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
@@ -705,7 +741,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -762,7 +798,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -820,7 +856,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -878,7 +914,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -936,7 +972,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -994,7 +1030,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1011,13 +1047,13 @@
         <v>25</v>
       </c>
       <c r="I7" t="n">
-        <v>7.16</v>
+        <v>42.12</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.91</v>
+        <v>36.96</v>
       </c>
       <c r="K7" t="n">
-        <v>3.59</v>
+        <v>21.59</v>
       </c>
       <c r="L7">
         <f>ROUND(SQRT((I7-I2)^2+(J7-J2)^2+(K7-K2)^2),2)</f>
@@ -1052,7 +1088,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1069,7 +1105,7 @@
         <v>27</v>
       </c>
       <c r="I8" t="n">
-        <v>44.01</v>
+        <v>42.01</v>
       </c>
       <c r="J8" t="n">
         <v>37.39</v>
@@ -1110,7 +1146,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1168,7 +1204,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1226,7 +1262,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1243,13 +1279,13 @@
         <v>37</v>
       </c>
       <c r="I11" t="n">
-        <v>47</v>
+        <v>42.87</v>
       </c>
       <c r="J11" t="n">
-        <v>30.2</v>
+        <v>36.32</v>
       </c>
       <c r="K11" t="n">
-        <v>20.15</v>
+        <v>22.12</v>
       </c>
       <c r="L11">
         <f>ROUND(SQRT((I11-I2)^2+(J11-J2)^2+(K11-K2)^2),2)</f>
@@ -1284,7 +1320,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1301,13 +1337,13 @@
         <v>41</v>
       </c>
       <c r="I12" t="n">
-        <v>47.36</v>
+        <v>42.46</v>
       </c>
       <c r="J12" t="n">
-        <v>30.06</v>
+        <v>36.77</v>
       </c>
       <c r="K12" t="n">
-        <v>18.62</v>
+        <v>22.62</v>
       </c>
       <c r="L12">
         <f>ROUND(SQRT((I12-I2)^2+(J12-J2)^2+(K12-K2)^2),2)</f>
@@ -1342,7 +1378,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1359,13 +1395,13 @@
         <v>53</v>
       </c>
       <c r="I13" t="n">
-        <v>48.09</v>
+        <v>43.75</v>
       </c>
       <c r="J13" t="n">
-        <v>29.97</v>
+        <v>36.78</v>
       </c>
       <c r="K13" t="n">
-        <v>15.1</v>
+        <v>21.62</v>
       </c>
       <c r="L13">
         <f>ROUND(SQRT((I13-I2)^2+(J13-J2)^2+(K13-K2)^2),2)</f>
@@ -1400,7 +1436,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1417,13 +1453,13 @@
         <v>57</v>
       </c>
       <c r="I14" t="n">
-        <v>44.88</v>
+        <v>42.88</v>
       </c>
       <c r="J14" t="n">
-        <v>32.75</v>
+        <v>36.75</v>
       </c>
       <c r="K14" t="n">
-        <v>19.94</v>
+        <v>21.92</v>
       </c>
       <c r="L14">
         <f>ROUND(SQRT((I14-I2)^2+(J14-J2)^2+(K14-K2)^2),2)</f>
@@ -1458,7 +1494,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1475,13 +1511,13 @@
         <v>61</v>
       </c>
       <c r="I15" t="n">
-        <v>45.4</v>
+        <v>43.42</v>
       </c>
       <c r="J15" t="n">
-        <v>33.23</v>
+        <v>36.23</v>
       </c>
       <c r="K15" t="n">
-        <v>19.7</v>
+        <v>21.71</v>
       </c>
       <c r="L15">
         <f>ROUND(SQRT((I15-I2)^2+(J15-J2)^2+(K15-K2)^2),2)</f>
@@ -1516,7 +1552,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1573,7 +1609,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1631,7 +1667,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1689,7 +1725,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1747,7 +1783,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1805,7 +1841,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1863,7 +1899,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1921,7 +1957,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1979,7 +2015,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2037,7 +2073,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2057,7 +2093,7 @@
         <v>45.48</v>
       </c>
       <c r="J25" t="n">
-        <v>33.48</v>
+        <v>36.48</v>
       </c>
       <c r="K25" t="n">
         <v>21.27</v>
@@ -2095,7 +2131,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2153,7 +2189,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2211,7 +2247,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2269,7 +2305,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2327,7 +2363,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2384,7 +2420,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2400,13 +2436,13 @@
       <c r="H31" t="n">
         <v>3</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31" s="4" t="n">
         <v>45.01</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" s="4" t="n">
         <v>35.63</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K31" s="4" t="n">
         <v>19.87</v>
       </c>
       <c r="L31">
@@ -2442,7 +2478,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2500,7 +2536,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2558,7 +2594,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2616,7 +2652,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2674,7 +2710,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2732,7 +2768,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2790,7 +2826,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2848,7 +2884,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2906,7 +2942,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2964,7 +3000,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3022,7 +3058,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3080,7 +3116,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3138,7 +3174,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3154,13 +3190,13 @@
       <c r="H44" t="n">
         <v>0</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44" s="4" t="n">
         <v>45.4</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" s="4" t="n">
         <v>36.54</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K44" s="4" t="n">
         <v>18.53</v>
       </c>
       <c r="L44" t="n">
@@ -3195,7 +3231,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3253,7 +3289,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3311,7 +3347,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3369,7 +3405,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3427,7 +3463,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3485,7 +3521,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3543,7 +3579,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3601,7 +3637,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3659,7 +3695,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3717,7 +3753,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3775,7 +3811,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3833,7 +3869,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3891,7 +3927,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3949,7 +3985,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3965,13 +4001,13 @@
       <c r="H58" t="n">
         <v>0</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I58" s="4" t="n">
         <v>46.72</v>
       </c>
-      <c r="J58" t="n">
+      <c r="J58" s="4" t="n">
         <v>37.64</v>
       </c>
-      <c r="K58" t="n">
+      <c r="K58" s="4" t="n">
         <v>21.16</v>
       </c>
       <c r="L58" t="n">
@@ -4006,7 +4042,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4064,7 +4100,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4122,7 +4158,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4180,7 +4216,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4238,7 +4274,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4296,7 +4332,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4354,7 +4390,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4412,7 +4448,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4470,7 +4506,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4528,7 +4564,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4586,7 +4622,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4644,7 +4680,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4702,7 +4738,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4760,7 +4796,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4776,13 +4812,13 @@
       <c r="H72" t="n">
         <v>0</v>
       </c>
-      <c r="I72" t="n">
+      <c r="I72" s="4" t="n">
         <v>47.45</v>
       </c>
-      <c r="J72" t="n">
+      <c r="J72" s="4" t="n">
         <v>35.56</v>
       </c>
-      <c r="K72" t="n">
+      <c r="K72" s="4" t="n">
         <v>18.73</v>
       </c>
       <c r="L72" t="n">
@@ -4817,7 +4853,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4875,7 +4911,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4895,7 +4931,7 @@
         <v>46.63</v>
       </c>
       <c r="J74" t="n">
-        <v>34.06</v>
+        <v>35.06</v>
       </c>
       <c r="K74" t="n">
         <v>17.65</v>
@@ -4933,7 +4969,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4950,13 +4986,13 @@
         <v>9</v>
       </c>
       <c r="I75" t="n">
-        <v>48.36</v>
+        <v>46.36</v>
       </c>
       <c r="J75" t="n">
-        <v>29.05</v>
+        <v>35.05</v>
       </c>
       <c r="K75" t="n">
-        <v>20.34</v>
+        <v>17.34</v>
       </c>
       <c r="L75">
         <f>ROUND(SQRT((I75-I72)^2+(J75-J72)^2+(K75-K72)^2),2)</f>
@@ -4991,7 +5027,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5049,7 +5085,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5069,10 +5105,10 @@
         <v>47.12</v>
       </c>
       <c r="J77" t="n">
-        <v>33.72</v>
+        <v>34.72</v>
       </c>
       <c r="K77" t="n">
-        <v>16.65</v>
+        <v>17.65</v>
       </c>
       <c r="L77">
         <f>ROUND(SQRT((I77-I72)^2+(J77-J72)^2+(K77-K72)^2),2)</f>
@@ -5107,7 +5143,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5165,7 +5201,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5223,7 +5259,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5243,7 +5279,7 @@
         <v>46.87</v>
       </c>
       <c r="J80" t="n">
-        <v>34.66</v>
+        <v>35.66</v>
       </c>
       <c r="K80" t="n">
         <v>17.04</v>
@@ -5281,7 +5317,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5301,7 +5337,7 @@
         <v>47.28</v>
       </c>
       <c r="J81" t="n">
-        <v>34.39</v>
+        <v>35.39</v>
       </c>
       <c r="K81" t="n">
         <v>17.12</v>
@@ -5339,7 +5375,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5359,10 +5395,10 @@
         <v>47.21</v>
       </c>
       <c r="J82" t="n">
-        <v>33.59</v>
+        <v>34.59</v>
       </c>
       <c r="K82" t="n">
-        <v>16.69</v>
+        <v>17.69</v>
       </c>
       <c r="L82">
         <f>ROUND(SQRT((I82-I72)^2+(J82-J72)^2+(K82-K72)^2),2)</f>
@@ -5397,7 +5433,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5455,7 +5491,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5472,10 +5508,10 @@
         <v>57</v>
       </c>
       <c r="I84" t="n">
-        <v>48.07</v>
+        <v>47.07</v>
       </c>
       <c r="J84" t="n">
-        <v>31.76</v>
+        <v>34.76</v>
       </c>
       <c r="K84" t="n">
         <v>17.51</v>
@@ -5513,7 +5549,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5571,7 +5607,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5587,13 +5623,13 @@
       <c r="H86" t="n">
         <v>0</v>
       </c>
-      <c r="I86" t="n">
+      <c r="I86" s="4" t="n">
         <v>46.45</v>
       </c>
-      <c r="J86" t="n">
+      <c r="J86" s="4" t="n">
         <v>36.05</v>
       </c>
-      <c r="K86" t="n">
+      <c r="K86" s="4" t="n">
         <v>19</v>
       </c>
       <c r="L86" t="n">
@@ -5628,7 +5664,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5686,7 +5722,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5706,7 +5742,7 @@
         <v>45.45</v>
       </c>
       <c r="J88" t="n">
-        <v>32.04</v>
+        <v>34.04</v>
       </c>
       <c r="K88" t="n">
         <v>17.34</v>
@@ -5744,7 +5780,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5802,7 +5838,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5860,7 +5896,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5918,7 +5954,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5976,7 +6012,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6034,7 +6070,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6092,7 +6128,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6150,7 +6186,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6208,7 +6244,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6266,7 +6302,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6324,7 +6360,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6382,7 +6418,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6398,13 +6434,13 @@
       <c r="H100" t="n">
         <v>0</v>
       </c>
-      <c r="I100" t="n">
+      <c r="I100" s="4" t="n">
         <v>48.16</v>
       </c>
-      <c r="J100" t="n">
+      <c r="J100" s="4" t="n">
         <v>35.74</v>
       </c>
-      <c r="K100" t="n">
+      <c r="K100" s="4" t="n">
         <v>19.65</v>
       </c>
       <c r="L100" t="n">
@@ -6439,7 +6475,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6497,7 +6533,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6555,7 +6591,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6613,7 +6649,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6671,7 +6707,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6729,7 +6765,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6787,7 +6823,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6845,7 +6881,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6903,7 +6939,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6961,7 +6997,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -7019,7 +7055,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7077,7 +7113,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7135,7 +7171,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7193,7 +7229,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7209,13 +7245,13 @@
       <c r="H114" t="n">
         <v>0</v>
       </c>
-      <c r="I114" t="n">
+      <c r="I114" s="4" t="n">
         <v>49.2</v>
       </c>
-      <c r="J114" t="n">
+      <c r="J114" s="4" t="n">
         <v>36.1</v>
       </c>
-      <c r="K114" t="n">
+      <c r="K114" s="4" t="n">
         <v>22.25</v>
       </c>
       <c r="L114" t="n">
@@ -7250,7 +7286,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7308,7 +7344,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7366,7 +7402,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7424,7 +7460,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -7444,10 +7480,10 @@
         <v>49.31</v>
       </c>
       <c r="J118" t="n">
-        <v>33.33</v>
+        <v>35.33</v>
       </c>
       <c r="K118" t="n">
-        <v>18.88</v>
+        <v>20.88</v>
       </c>
       <c r="L118">
         <f>ROUND(SQRT((I118-I114)^2+(J118-J114)^2+(K118-K114)^2),2)</f>
@@ -7482,7 +7518,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7502,10 +7538,10 @@
         <v>49.61</v>
       </c>
       <c r="J119" t="n">
-        <v>33.68</v>
+        <v>35.68</v>
       </c>
       <c r="K119" t="n">
-        <v>18.41</v>
+        <v>20.41</v>
       </c>
       <c r="L119">
         <f>ROUND(SQRT((I119-I114)^2+(J119-J114)^2+(K119-K114)^2),2)</f>
@@ -7540,7 +7576,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7560,10 +7596,10 @@
         <v>49.76</v>
       </c>
       <c r="J120" t="n">
-        <v>33.11</v>
+        <v>35.11</v>
       </c>
       <c r="K120" t="n">
-        <v>18.69</v>
+        <v>20.69</v>
       </c>
       <c r="L120">
         <f>ROUND(SQRT((I120-I114)^2+(J120-J114)^2+(K120-K114)^2),2)</f>
@@ -7598,7 +7634,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7618,10 +7654,10 @@
         <v>49.91</v>
       </c>
       <c r="J121" t="n">
-        <v>32.14</v>
+        <v>35.14</v>
       </c>
       <c r="K121" t="n">
-        <v>16.65</v>
+        <v>20.65</v>
       </c>
       <c r="L121">
         <f>ROUND(SQRT((I121-I114)^2+(J121-J114)^2+(K121-K114)^2),2)</f>
@@ -7656,7 +7692,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7673,13 +7709,13 @@
         <v>34</v>
       </c>
       <c r="I122" t="n">
-        <v>49.88</v>
+        <v>48.88</v>
       </c>
       <c r="J122" t="n">
-        <v>32.48</v>
+        <v>35.48</v>
       </c>
       <c r="K122" t="n">
-        <v>19.44</v>
+        <v>20.44</v>
       </c>
       <c r="L122">
         <f>ROUND(SQRT((I122-I114)^2+(J122-J114)^2+(K122-K114)^2),2)</f>
@@ -7714,7 +7750,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -7734,10 +7770,10 @@
         <v>48.96</v>
       </c>
       <c r="J123" t="n">
-        <v>34.82</v>
+        <v>35.82</v>
       </c>
       <c r="K123" t="n">
-        <v>19.06</v>
+        <v>20.06</v>
       </c>
       <c r="L123">
         <f>ROUND(SQRT((I123-I114)^2+(J123-J114)^2+(K123-K114)^2),2)</f>
@@ -7772,7 +7808,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -7789,13 +7825,13 @@
         <v>41</v>
       </c>
       <c r="I124" t="n">
-        <v>49.22</v>
+        <v>48.22</v>
       </c>
       <c r="J124" t="n">
-        <v>32.7</v>
+        <v>35.7</v>
       </c>
       <c r="K124" t="n">
-        <v>18.21</v>
+        <v>20.21</v>
       </c>
       <c r="L124">
         <f>ROUND(SQRT((I124-I114)^2+(J124-J114)^2+(K124-K114)^2),2)</f>
@@ -7830,7 +7866,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -7853,7 +7889,7 @@
         <v>35.05</v>
       </c>
       <c r="K125" t="n">
-        <v>19.21</v>
+        <v>20.21</v>
       </c>
       <c r="L125">
         <f>ROUND(SQRT((I125-I114)^2+(J125-J114)^2+(K125-K114)^2),2)</f>
@@ -7888,7 +7924,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7908,7 +7944,7 @@
         <v>48.85</v>
       </c>
       <c r="J126" t="n">
-        <v>34.46</v>
+        <v>35.16</v>
       </c>
       <c r="K126" t="n">
         <v>20.14</v>
@@ -7946,7 +7982,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -8004,7 +8040,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -8020,13 +8056,13 @@
       <c r="H128" t="n">
         <v>0</v>
       </c>
-      <c r="I128" t="n">
+      <c r="I128" s="4" t="n">
         <v>51.68</v>
       </c>
-      <c r="J128" t="n">
+      <c r="J128" s="4" t="n">
         <v>34.77</v>
       </c>
-      <c r="K128" t="n">
+      <c r="K128" s="4" t="n">
         <v>21.18</v>
       </c>
       <c r="L128" t="n">
@@ -8061,7 +8097,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -8119,7 +8155,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8177,7 +8213,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8235,7 +8271,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8293,7 +8329,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8351,7 +8387,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -8409,7 +8445,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8467,7 +8503,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8525,7 +8561,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -8583,7 +8619,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -8641,7 +8677,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -8699,7 +8735,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -8757,7 +8793,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8804,7 +8840,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M141"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -8814,9 +8850,7 @@
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="9" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
@@ -8911,7 +8945,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -8927,13 +8961,13 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="4" t="n">
         <v>60.38</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="4" t="n">
         <v>-31.49</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="4" t="n">
         <v>15.09</v>
       </c>
       <c r="L2" t="n">
@@ -8968,7 +9002,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -9026,7 +9060,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -9084,7 +9118,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -9142,7 +9176,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -9200,7 +9234,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -9258,7 +9292,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -9316,7 +9350,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -9374,7 +9408,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -9432,7 +9466,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -9490,7 +9524,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -9548,7 +9582,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -9606,7 +9640,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -9664,7 +9698,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -9722,7 +9756,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -9738,13 +9772,13 @@
       <c r="H16" t="n">
         <v>0</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="4" t="n">
         <v>59.98</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="4" t="n">
         <v>-32.59</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="4" t="n">
         <v>14.98</v>
       </c>
       <c r="L16" t="n">
@@ -9779,7 +9813,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -9837,7 +9871,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -9895,7 +9929,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -9953,7 +9987,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -10011,7 +10045,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -10069,7 +10103,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -10127,7 +10161,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -10185,7 +10219,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -10243,7 +10277,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -10301,7 +10335,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -10359,7 +10393,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -10417,7 +10451,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -10475,7 +10509,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -10533,7 +10567,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -10549,13 +10583,13 @@
       <c r="H30" t="n">
         <v>0</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" s="4" t="n">
         <v>61.84</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" s="4" t="n">
         <v>-30.81</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30" s="4" t="n">
         <v>14.68</v>
       </c>
       <c r="L30" t="n">
@@ -10590,7 +10624,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -10648,7 +10682,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -10706,7 +10740,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -10764,7 +10798,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -10822,7 +10856,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -10880,7 +10914,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -10938,7 +10972,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -10996,7 +11030,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -11054,7 +11088,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -11112,7 +11146,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -11170,7 +11204,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -11228,7 +11262,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -11286,7 +11320,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -11344,7 +11378,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -11360,13 +11394,13 @@
       <c r="H44" t="n">
         <v>0</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44" s="4" t="n">
         <v>62.65</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" s="4" t="n">
         <v>-28.79</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K44" s="4" t="n">
         <v>13.52</v>
       </c>
       <c r="L44" t="n">
@@ -11401,7 +11435,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -11459,7 +11493,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -11517,7 +11551,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -11575,7 +11609,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -11633,7 +11667,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -11691,7 +11725,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -11749,7 +11783,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -11807,7 +11841,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -11865,7 +11899,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -11923,7 +11957,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -11981,7 +12015,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -12039,7 +12073,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -12059,7 +12093,7 @@
         <v>62.73</v>
       </c>
       <c r="J56" t="n">
-        <v>29.24</v>
+        <v>-29.24</v>
       </c>
       <c r="K56" t="n">
         <v>13.62</v>
@@ -12097,7 +12131,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -12113,13 +12147,13 @@
       <c r="H57" t="n">
         <v>61</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I57" s="4" t="n">
         <v>62.5</v>
       </c>
-      <c r="J57" t="n">
+      <c r="J57" s="4" t="n">
         <v>-27.41</v>
       </c>
-      <c r="K57" t="n">
+      <c r="K57" s="4" t="n">
         <v>12.08</v>
       </c>
       <c r="L57">
@@ -12155,7 +12189,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -12212,7 +12246,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -12270,7 +12304,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -12328,7 +12362,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12386,7 +12420,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12444,7 +12478,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12502,7 +12536,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12560,7 +12594,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12618,7 +12652,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12676,7 +12710,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12734,7 +12768,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12792,7 +12826,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -12850,7 +12884,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -12908,7 +12942,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -12966,7 +13000,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -12982,13 +13016,13 @@
       <c r="H72" t="n">
         <v>0</v>
       </c>
-      <c r="I72" t="n">
+      <c r="I72" s="4" t="n">
         <v>59.82</v>
       </c>
-      <c r="J72" t="n">
+      <c r="J72" s="4" t="n">
         <v>-31.73</v>
       </c>
-      <c r="K72" t="n">
+      <c r="K72" s="4" t="n">
         <v>15.24</v>
       </c>
       <c r="L72" t="n">
@@ -13023,7 +13057,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13081,7 +13115,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -13139,7 +13173,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -13197,7 +13231,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -13255,7 +13289,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -13313,7 +13347,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -13371,7 +13405,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -13429,7 +13463,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -13487,7 +13521,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -13545,7 +13579,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -13603,7 +13637,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -13661,7 +13695,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -13719,7 +13753,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -13777,7 +13811,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -13793,13 +13827,13 @@
       <c r="H86" t="n">
         <v>0</v>
       </c>
-      <c r="I86" t="n">
+      <c r="I86" s="4" t="n">
         <v>59.27</v>
       </c>
-      <c r="J86" t="n">
+      <c r="J86" s="4" t="n">
         <v>-32.38</v>
       </c>
-      <c r="K86" t="n">
+      <c r="K86" s="4" t="n">
         <v>14.74</v>
       </c>
       <c r="L86" t="n">
@@ -13834,7 +13868,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -13892,7 +13926,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -13950,7 +13984,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -14008,7 +14042,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -14066,7 +14100,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -14124,7 +14158,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -14182,7 +14216,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -14240,7 +14274,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -14298,7 +14332,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -14356,7 +14390,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -14414,7 +14448,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -14472,7 +14506,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -14530,7 +14564,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -14588,7 +14622,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -14604,13 +14638,13 @@
       <c r="H100" t="n">
         <v>0</v>
       </c>
-      <c r="I100" t="n">
+      <c r="I100" s="4" t="n">
         <v>58.98</v>
       </c>
-      <c r="J100" t="n">
+      <c r="J100" s="4" t="n">
         <v>-32.05</v>
       </c>
-      <c r="K100" t="n">
+      <c r="K100" s="4" t="n">
         <v>15.98</v>
       </c>
       <c r="L100" t="n">
@@ -14645,7 +14679,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -14662,13 +14696,13 @@
         <v>3</v>
       </c>
       <c r="I101" t="n">
-        <v>61.11</v>
+        <v>58.11</v>
       </c>
       <c r="J101" t="n">
-        <v>-28.67</v>
+        <v>-31.67</v>
       </c>
       <c r="K101" t="n">
-        <v>12.9</v>
+        <v>14.9</v>
       </c>
       <c r="L101">
         <f>ROUND(SQRT((I101-I100)^2+(J101-J100)^2+(K101-K100)^2),2)</f>
@@ -14703,7 +14737,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -14761,7 +14795,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -14778,13 +14812,13 @@
         <v>9</v>
       </c>
       <c r="I103" t="n">
-        <v>60</v>
+        <v>58.57</v>
       </c>
       <c r="J103" t="n">
         <v>-31.45</v>
       </c>
       <c r="K103" t="n">
-        <v>12.44</v>
+        <v>14.44</v>
       </c>
       <c r="L103">
         <f>ROUND(SQRT((I103-I100)^2+(J103-J100)^2+(K103-K100)^2),2)</f>
@@ -14819,7 +14853,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -14877,7 +14911,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -14894,13 +14928,13 @@
         <v>25</v>
       </c>
       <c r="I105" t="n">
-        <v>60.87</v>
+        <v>58.87</v>
       </c>
       <c r="J105" t="n">
-        <v>-29.81</v>
+        <v>-31.81</v>
       </c>
       <c r="K105" t="n">
-        <v>17.41</v>
+        <v>14.41</v>
       </c>
       <c r="L105">
         <f>ROUND(SQRT((I105-I100)^2+(J105-J100)^2+(K105-K100)^2),2)</f>
@@ -14935,7 +14969,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -14952,13 +14986,13 @@
         <v>27</v>
       </c>
       <c r="I106" t="n">
-        <v>60.6</v>
+        <v>58.6</v>
       </c>
       <c r="J106" t="n">
-        <v>-30.26</v>
+        <v>-31.26</v>
       </c>
       <c r="K106" t="n">
-        <v>13.88</v>
+        <v>14.88</v>
       </c>
       <c r="L106">
         <f>ROUND(SQRT((I106-I100)^2+(J106-J100)^2+(K106-K100)^2),2)</f>
@@ -14993,7 +15027,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -15051,7 +15085,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -15071,10 +15105,10 @@
         <v>59.23</v>
       </c>
       <c r="J108" t="n">
-        <v>-30.81</v>
+        <v>-31.81</v>
       </c>
       <c r="K108" t="n">
-        <v>13.02</v>
+        <v>14.02</v>
       </c>
       <c r="L108">
         <f>ROUND(SQRT((I108-I100)^2+(J108-J100)^2+(K108-K100)^2),2)</f>
@@ -15109,7 +15143,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -15167,7 +15201,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -15225,7 +15259,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -15283,7 +15317,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -15300,10 +15334,10 @@
         <v>57</v>
       </c>
       <c r="I112" t="n">
-        <v>62.1</v>
+        <v>59.21</v>
       </c>
       <c r="J112" t="n">
-        <v>-24.81</v>
+        <v>-31.81</v>
       </c>
       <c r="K112" t="n">
         <v>14.22</v>
@@ -15341,7 +15375,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -15399,7 +15433,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -15415,13 +15449,13 @@
       <c r="H114" t="n">
         <v>0</v>
       </c>
-      <c r="I114" t="n">
+      <c r="I114" s="4" t="n">
         <v>59.81</v>
       </c>
-      <c r="J114" t="n">
+      <c r="J114" s="4" t="n">
         <v>-32.16</v>
       </c>
-      <c r="K114" t="n">
+      <c r="K114" s="4" t="n">
         <v>15.73</v>
       </c>
       <c r="L114" t="n">
@@ -15456,7 +15490,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -15514,7 +15548,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -15572,7 +15606,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -15630,7 +15664,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -15647,7 +15681,7 @@
         <v>12</v>
       </c>
       <c r="I118" t="n">
-        <v>61.57</v>
+        <v>59.57</v>
       </c>
       <c r="J118" t="n">
         <v>-31.24</v>
@@ -15688,7 +15722,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -15705,13 +15739,13 @@
         <v>25</v>
       </c>
       <c r="I119" t="n">
-        <v>61.32</v>
+        <v>59.32</v>
       </c>
       <c r="J119" t="n">
-        <v>-30.38</v>
+        <v>-31.38</v>
       </c>
       <c r="K119" t="n">
-        <v>13.55</v>
+        <v>14.55</v>
       </c>
       <c r="L119">
         <f>ROUND(SQRT((I119-I114)^2+(J119-J114)^2+(K119-K114)^2),2)</f>
@@ -15746,7 +15780,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -15766,10 +15800,10 @@
         <v>59.64</v>
       </c>
       <c r="J120" t="n">
-        <v>-30</v>
+        <v>-30.32</v>
       </c>
       <c r="K120" t="n">
-        <v>13.13</v>
+        <v>14.73</v>
       </c>
       <c r="L120">
         <f>ROUND(SQRT((I120-I114)^2+(J120-J114)^2+(K120-K114)^2),2)</f>
@@ -15804,7 +15838,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -15821,13 +15855,13 @@
         <v>31</v>
       </c>
       <c r="I121" t="n">
-        <v>61.22</v>
+        <v>59.22</v>
       </c>
       <c r="J121" t="n">
-        <v>-29.63</v>
+        <v>-30.63</v>
       </c>
       <c r="K121" t="n">
-        <v>13.25</v>
+        <v>14.25</v>
       </c>
       <c r="L121">
         <f>ROUND(SQRT((I121-I114)^2+(J121-J114)^2+(K121-K114)^2),2)</f>
@@ -15862,7 +15896,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -15879,7 +15913,7 @@
         <v>34</v>
       </c>
       <c r="I122" t="n">
-        <v>61.63</v>
+        <v>59.63</v>
       </c>
       <c r="J122" t="n">
         <v>-30.57</v>
@@ -15920,7 +15954,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -15937,13 +15971,13 @@
         <v>37</v>
       </c>
       <c r="I123" t="n">
-        <v>61.5</v>
+        <v>59.5</v>
       </c>
       <c r="J123" t="n">
         <v>-30.27</v>
       </c>
       <c r="K123" t="n">
-        <v>13.3</v>
+        <v>14.39</v>
       </c>
       <c r="L123">
         <f>ROUND(SQRT((I123-I114)^2+(J123-J114)^2+(K123-K114)^2),2)</f>
@@ -15978,7 +16012,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -15995,13 +16029,13 @@
         <v>41</v>
       </c>
       <c r="I124" t="n">
-        <v>60.76</v>
+        <v>59.76</v>
       </c>
       <c r="J124" t="n">
         <v>-30.53</v>
       </c>
       <c r="K124" t="n">
-        <v>13.27</v>
+        <v>14.27</v>
       </c>
       <c r="L124">
         <f>ROUND(SQRT((I124-I114)^2+(J124-J114)^2+(K124-K114)^2),2)</f>
@@ -16036,7 +16070,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -16053,7 +16087,7 @@
         <v>53</v>
       </c>
       <c r="I125" t="n">
-        <v>60.12</v>
+        <v>59.12</v>
       </c>
       <c r="J125" t="n">
         <v>-30.71</v>
@@ -16094,7 +16128,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -16111,7 +16145,7 @@
         <v>57</v>
       </c>
       <c r="I126" t="n">
-        <v>61.51</v>
+        <v>59.51</v>
       </c>
       <c r="J126" t="n">
         <v>-30.83</v>
@@ -16152,7 +16186,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -16169,7 +16203,7 @@
         <v>61</v>
       </c>
       <c r="I127" t="n">
-        <v>61.12</v>
+        <v>59.12</v>
       </c>
       <c r="J127" t="n">
         <v>-30.77</v>
@@ -16210,7 +16244,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -16226,13 +16260,13 @@
       <c r="H128" t="n">
         <v>0</v>
       </c>
-      <c r="I128" t="n">
+      <c r="I128" s="4" t="n">
         <v>62.84</v>
       </c>
-      <c r="J128" t="n">
+      <c r="J128" s="4" t="n">
         <v>-30.47</v>
       </c>
-      <c r="K128" t="n">
+      <c r="K128" s="4" t="n">
         <v>13.9</v>
       </c>
       <c r="L128" t="n">
@@ -16267,7 +16301,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -16325,7 +16359,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -16345,7 +16379,7 @@
         <v>62.73</v>
       </c>
       <c r="J130" t="n">
-        <v>-19.99</v>
+        <v>-29.99</v>
       </c>
       <c r="K130" t="n">
         <v>14.04</v>
@@ -16383,7 +16417,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -16441,7 +16475,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -16499,7 +16533,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -16557,7 +16591,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -16615,7 +16649,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -16673,7 +16707,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -16731,7 +16765,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -16789,7 +16823,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -16847,7 +16881,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -16905,7 +16939,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -16925,10 +16959,10 @@
         <v>62.49</v>
       </c>
       <c r="J140" t="n">
-        <v>-27.89</v>
+        <v>-29.89</v>
       </c>
       <c r="K140" t="n">
-        <v>12.83</v>
+        <v>13.83</v>
       </c>
       <c r="L140">
         <f>ROUND(SQRT((I140-I128)^2+(J140-J128)^2+(K140-K128)^2),2)</f>
@@ -16963,7 +16997,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -17010,7 +17044,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M141"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -17020,9 +17054,7 @@
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="9" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
@@ -17117,7 +17149,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -17133,13 +17165,13 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="4" t="n">
         <v>40.55</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="4" t="n">
         <v>-5.53</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="4" t="n">
         <v>-29.13</v>
       </c>
       <c r="L2" t="n">
@@ -17174,7 +17206,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -17232,7 +17264,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -17290,7 +17322,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -17348,7 +17380,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -17406,7 +17438,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -17423,10 +17455,10 @@
         <v>25</v>
       </c>
       <c r="I7" t="n">
-        <v>41.18</v>
+        <v>40.18</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.72</v>
+        <v>-4.72</v>
       </c>
       <c r="K7" t="n">
         <v>-30.74</v>
@@ -17464,7 +17496,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -17481,7 +17513,7 @@
         <v>27</v>
       </c>
       <c r="I8" t="n">
-        <v>43.07</v>
+        <v>41.07</v>
       </c>
       <c r="J8" t="n">
         <v>-5.57</v>
@@ -17522,7 +17554,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -17542,7 +17574,7 @@
         <v>41.09</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.58</v>
+        <v>-4.58</v>
       </c>
       <c r="K9" t="n">
         <v>-30.63</v>
@@ -17580,7 +17612,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -17638,7 +17670,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -17696,7 +17728,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -17754,7 +17786,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -17812,7 +17844,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -17870,7 +17902,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -17928,7 +17960,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -17944,13 +17976,13 @@
       <c r="H16" t="n">
         <v>0</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="4" t="n">
         <v>38.55</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="4" t="n">
         <v>-4.49</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="4" t="n">
         <v>-30.63</v>
       </c>
       <c r="L16" t="n">
@@ -17985,7 +18017,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -18043,7 +18075,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -18101,7 +18133,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -18159,7 +18191,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -18217,7 +18249,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -18275,7 +18307,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -18333,7 +18365,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -18391,7 +18423,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -18449,7 +18481,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -18507,7 +18539,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -18565,7 +18597,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -18623,7 +18655,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -18681,7 +18713,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -18739,7 +18771,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -18755,13 +18787,13 @@
       <c r="H30" t="n">
         <v>0</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" s="4" t="n">
         <v>41.14</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" s="4" t="n">
         <v>-5.7</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30" s="4" t="n">
         <v>-29.66</v>
       </c>
       <c r="L30" t="n">
@@ -18796,7 +18828,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -18854,7 +18886,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -18912,7 +18944,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -18970,7 +19002,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -19028,7 +19060,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -19086,7 +19118,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -19144,7 +19176,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -19202,7 +19234,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -19260,7 +19292,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -19318,7 +19350,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -19376,7 +19408,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -19434,7 +19466,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -19492,7 +19524,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -19550,7 +19582,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -19566,13 +19598,13 @@
       <c r="H44" t="n">
         <v>0</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44" s="4" t="n">
         <v>41.84</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" s="4" t="n">
         <v>-6.58</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K44" s="4" t="n">
         <v>-27.86</v>
       </c>
       <c r="L44" t="n">
@@ -19607,7 +19639,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -19665,7 +19697,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -19723,7 +19755,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -19781,7 +19813,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -19839,7 +19871,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -19897,7 +19929,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -19955,7 +19987,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -20013,7 +20045,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -20071,7 +20103,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -20129,7 +20161,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -20187,7 +20219,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -20204,13 +20236,13 @@
         <v>53</v>
       </c>
       <c r="I55" t="n">
-        <v>45.24</v>
+        <v>43.24</v>
       </c>
       <c r="J55" t="n">
         <v>-5.61</v>
       </c>
       <c r="K55" t="n">
-        <v>-24.17</v>
+        <v>-27.17</v>
       </c>
       <c r="L55">
         <f>ROUND(SQRT((I55-I44)^2+(J55-J44)^2+(K55-K44)^2),2)</f>
@@ -20245,7 +20277,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -20268,7 +20300,7 @@
         <v>-6.69</v>
       </c>
       <c r="K56" t="n">
-        <v>-24.64</v>
+        <v>-27.64</v>
       </c>
       <c r="L56">
         <f>ROUND(SQRT((I56-I44)^2+(J56-J44)^2+(K56-K44)^2),2)</f>
@@ -20303,7 +20335,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -20361,7 +20393,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -20377,13 +20409,13 @@
       <c r="H58" t="n">
         <v>0</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I58" s="4" t="n">
         <v>39.5</v>
       </c>
-      <c r="J58" t="n">
+      <c r="J58" s="4" t="n">
         <v>-5.82</v>
       </c>
-      <c r="K58" t="n">
+      <c r="K58" s="4" t="n">
         <v>-29.2</v>
       </c>
       <c r="L58" t="n">
@@ -20418,7 +20450,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -20476,7 +20508,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -20534,7 +20566,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -20592,7 +20624,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -20650,7 +20682,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -20708,7 +20740,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -20766,7 +20798,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -20824,7 +20856,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -20882,7 +20914,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -20940,7 +20972,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -20998,7 +21030,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -21056,7 +21088,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -21114,7 +21146,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -21172,7 +21204,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -21188,13 +21220,13 @@
       <c r="H72" t="n">
         <v>0</v>
       </c>
-      <c r="I72" t="n">
+      <c r="I72" s="4" t="n">
         <v>41.4</v>
       </c>
-      <c r="J72" t="n">
+      <c r="J72" s="4" t="n">
         <v>-5.3</v>
       </c>
-      <c r="K72" t="n">
+      <c r="K72" s="4" t="n">
         <v>-32.75</v>
       </c>
       <c r="L72" t="n">
@@ -21229,7 +21261,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -21287,7 +21319,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -21345,7 +21377,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -21403,7 +21435,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -21461,7 +21493,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -21519,7 +21551,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -21577,7 +21609,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -21635,7 +21667,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -21693,7 +21725,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -21751,7 +21783,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -21767,13 +21799,13 @@
       <c r="H82" t="n">
         <v>41</v>
       </c>
-      <c r="I82" t="n">
+      <c r="I82" s="5" t="n">
         <v>42.22</v>
       </c>
-      <c r="J82" t="n">
+      <c r="J82" s="5" t="n">
         <v>-6.45</v>
       </c>
-      <c r="K82" t="n">
+      <c r="K82" s="5" t="n">
         <v>-31.34</v>
       </c>
       <c r="L82">
@@ -21809,7 +21841,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -21867,7 +21899,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -21925,7 +21957,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -21983,7 +22015,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -21999,13 +22031,13 @@
       <c r="H86" t="n">
         <v>0</v>
       </c>
-      <c r="I86" t="n">
+      <c r="I86" s="4" t="n">
         <v>40.51</v>
       </c>
-      <c r="J86" t="n">
+      <c r="J86" s="4" t="n">
         <v>-4.94</v>
       </c>
-      <c r="K86" t="n">
+      <c r="K86" s="4" t="n">
         <v>-33.11</v>
       </c>
       <c r="L86" t="n">
@@ -22040,7 +22072,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -22098,7 +22130,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -22156,7 +22188,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -22214,7 +22246,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -22272,7 +22304,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -22330,7 +22362,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -22388,7 +22420,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -22446,7 +22478,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -22504,7 +22536,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -22562,7 +22594,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -22620,7 +22652,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -22637,10 +22669,10 @@
         <v>53</v>
       </c>
       <c r="I97" t="n">
-        <v>42.6</v>
+        <v>40.6</v>
       </c>
       <c r="J97" t="n">
-        <v>-6.98</v>
+        <v>-4.98</v>
       </c>
       <c r="K97" t="n">
         <v>-32.18</v>
@@ -22678,7 +22710,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -22736,7 +22768,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -22753,10 +22785,10 @@
         <v>61</v>
       </c>
       <c r="I99" t="n">
-        <v>42.02</v>
+        <v>40.02</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.51</v>
+        <v>-4.51</v>
       </c>
       <c r="K99" t="n">
         <v>-33.4</v>
@@ -22794,7 +22826,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -22810,13 +22842,13 @@
       <c r="H100" t="n">
         <v>0</v>
       </c>
-      <c r="I100" t="n">
+      <c r="I100" s="4" t="n">
         <v>40.61</v>
       </c>
-      <c r="J100" t="n">
+      <c r="J100" s="4" t="n">
         <v>-5.44</v>
       </c>
-      <c r="K100" t="n">
+      <c r="K100" s="4" t="n">
         <v>-32.22</v>
       </c>
       <c r="L100" t="n">
@@ -22851,7 +22883,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -22909,7 +22941,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -22967,7 +22999,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -23025,7 +23057,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -23083,7 +23115,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -23141,7 +23173,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -23199,7 +23231,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -23257,7 +23289,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -23280,7 +23312,7 @@
         <v>-5.29</v>
       </c>
       <c r="K108" t="n">
-        <v>-30.28</v>
+        <v>-31.28</v>
       </c>
       <c r="L108">
         <f>ROUND(SQRT((I108-I100)^2+(J108-J100)^2+(K108-K100)^2),2)</f>
@@ -23315,7 +23347,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -23338,7 +23370,7 @@
         <v>-4.54</v>
       </c>
       <c r="K109" t="n">
-        <v>-27.04</v>
+        <v>-31.04</v>
       </c>
       <c r="L109">
         <f>ROUND(SQRT((I109-I100)^2+(J109-J100)^2+(K109-K100)^2),2)</f>
@@ -23373,7 +23405,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -23431,7 +23463,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -23489,7 +23521,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -23547,7 +23579,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -23605,7 +23637,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -23621,13 +23653,13 @@
       <c r="H114" t="n">
         <v>0</v>
       </c>
-      <c r="I114" t="n">
+      <c r="I114" s="4" t="n">
         <v>41.17</v>
       </c>
-      <c r="J114" t="n">
+      <c r="J114" s="4" t="n">
         <v>-4.12</v>
       </c>
-      <c r="K114" t="n">
+      <c r="K114" s="4" t="n">
         <v>-28.95</v>
       </c>
       <c r="L114" t="n">
@@ -23662,7 +23694,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -23720,7 +23752,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -23778,7 +23810,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -23836,7 +23868,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -23856,10 +23888,10 @@
         <v>41.4</v>
       </c>
       <c r="J118" t="n">
-        <v>-6.64</v>
+        <v>-4.64</v>
       </c>
       <c r="K118" t="n">
-        <v>-25.92</v>
+        <v>-27.92</v>
       </c>
       <c r="L118">
         <f>ROUND(SQRT((I118-I114)^2+(J118-J114)^2+(K118-K114)^2),2)</f>
@@ -23894,7 +23926,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -23952,7 +23984,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -23975,7 +24007,7 @@
         <v>-6.21</v>
       </c>
       <c r="K120" t="n">
-        <v>-26</v>
+        <v>-27.12</v>
       </c>
       <c r="L120">
         <f>ROUND(SQRT((I120-I114)^2+(J120-J114)^2+(K120-K114)^2),2)</f>
@@ -24010,7 +24042,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -24068,7 +24100,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -24126,7 +24158,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -24184,7 +24216,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -24201,13 +24233,13 @@
         <v>41</v>
       </c>
       <c r="I124" t="n">
-        <v>43.13</v>
+        <v>41.13</v>
       </c>
       <c r="J124" t="n">
         <v>-5.23</v>
       </c>
       <c r="K124" t="n">
-        <v>-26.62</v>
+        <v>-27.62</v>
       </c>
       <c r="L124">
         <f>ROUND(SQRT((I124-I114)^2+(J124-J114)^2+(K124-K114)^2),2)</f>
@@ -24242,7 +24274,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -24262,10 +24294,10 @@
         <v>42.83</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.98</v>
+        <v>-4.98</v>
       </c>
       <c r="K125" t="n">
-        <v>-23.91</v>
+        <v>-27.91</v>
       </c>
       <c r="L125">
         <f>ROUND(SQRT((I125-I114)^2+(J125-J114)^2+(K125-K114)^2),2)</f>
@@ -24300,7 +24332,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -24320,10 +24352,10 @@
         <v>42.63</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.77</v>
+        <v>-4.77</v>
       </c>
       <c r="K126" t="n">
-        <v>-24.02</v>
+        <v>-27.02</v>
       </c>
       <c r="L126">
         <f>ROUND(SQRT((I126-I114)^2+(J126-J114)^2+(K126-K114)^2),2)</f>
@@ -24358,7 +24390,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -24416,7 +24448,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -24432,13 +24464,13 @@
       <c r="H128" t="n">
         <v>0</v>
       </c>
-      <c r="I128" t="n">
+      <c r="I128" s="4" t="n">
         <v>39.08</v>
       </c>
-      <c r="J128" t="n">
+      <c r="J128" s="4" t="n">
         <v>-6.04</v>
       </c>
-      <c r="K128" t="n">
+      <c r="K128" s="4" t="n">
         <v>-28.25</v>
       </c>
       <c r="L128" t="n">
@@ -24473,7 +24505,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -24496,7 +24528,7 @@
         <v>-6.68</v>
       </c>
       <c r="K129" t="n">
-        <v>-23.37</v>
+        <v>-27.37</v>
       </c>
       <c r="L129">
         <f>ROUND(SQRT((I129-I128)^2+(J129-J128)^2+(K129-K128)^2),2)</f>
@@ -24531,7 +24563,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -24589,7 +24621,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -24647,7 +24679,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -24664,13 +24696,13 @@
         <v>12</v>
       </c>
       <c r="I132" t="n">
-        <v>35.59</v>
+        <v>37.59</v>
       </c>
       <c r="J132" t="n">
         <v>-6.35</v>
       </c>
       <c r="K132" t="n">
-        <v>-29.47</v>
+        <v>-27.47</v>
       </c>
       <c r="L132">
         <f>ROUND(SQRT((I132-I128)^2+(J132-J128)^2+(K132-K128)^2),2)</f>
@@ -24705,7 +24737,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -24763,7 +24795,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -24821,7 +24853,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -24879,7 +24911,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -24937,7 +24969,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -24995,7 +25027,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -25053,7 +25085,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -25111,7 +25143,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -25169,7 +25201,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
